--- a/mosip_master/xlsx/loc_holiday.xlsx
+++ b/mosip_master/xlsx/loc_holiday.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nicholas\Desktop\NIRA MASTERDATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karthik.s\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BC9506B-0170-4479-B932-23DBF47569C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE64D0D9-E5D4-4BC7-8E34-415937DC94D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B60B003D-176B-49C1-9EFF-87A9FC258896}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{ABB48F84-6EC1-4FCC-8100-E70AED6E0E2D}"/>
   </bookViews>
   <sheets>
-    <sheet name="loc_holiday" sheetId="1" r:id="rId1"/>
+    <sheet name="loc_holiday_202504151201" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="33">
   <si>
     <t>id</t>
   </si>
@@ -64,7 +64,7 @@
     <t>UGA</t>
   </si>
   <si>
-    <t>Easter Sunday</t>
+    <t>New Year</t>
   </si>
   <si>
     <t>National Holiday</t>
@@ -73,13 +73,40 @@
     <t>eng</t>
   </si>
   <si>
-    <t>f</t>
+    <t>globaladmin</t>
   </si>
   <si>
-    <t>zimbe</t>
+    <t>Liberation Day</t>
   </si>
   <si>
-    <t>globaladmin</t>
+    <t>Remembrance of Archbishop Janani Luwum</t>
+  </si>
+  <si>
+    <t>International Women's Day</t>
+  </si>
+  <si>
+    <t>Eid al-Fitr</t>
+  </si>
+  <si>
+    <t>Good Friday</t>
+  </si>
+  <si>
+    <t>Easter Sunday</t>
+  </si>
+  <si>
+    <t>Easter Monday</t>
+  </si>
+  <si>
+    <t>Labour Day</t>
+  </si>
+  <si>
+    <t>Martyrs' Day</t>
+  </si>
+  <si>
+    <t>Eid al-Adha</t>
+  </si>
+  <si>
+    <t>National Heroes Day</t>
   </si>
   <si>
     <t>Independence Day</t>
@@ -88,10 +115,10 @@
     <t>Christmas Day</t>
   </si>
   <si>
-    <t>Eid Adha</t>
+    <t>Boxing Day</t>
   </si>
   <si>
-    <t>New Year's Day</t>
+    <t>now()</t>
   </si>
 </sst>
 </file>
@@ -953,11 +980,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09C7B2E9-DE8D-4DE6-BAAD-C049F84FB53A}">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90FC5A3F-9D36-4610-9275-A689EFB249D0}">
+  <dimension ref="A1:M76"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -998,15 +1025,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>2000002</v>
+        <v>2000001</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
       </c>
       <c r="C2" s="1">
-        <v>45383</v>
+        <v>45658</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -1017,175 +1044,2385 @@
       <c r="F2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" t="s">
-        <v>17</v>
+      <c r="G2" t="b">
+        <v>1</v>
       </c>
       <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2000002</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1">
+        <v>45683</v>
+      </c>
+      <c r="D3" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="2">
-        <v>45343.546183009261</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2000003</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1">
+        <v>45704</v>
+      </c>
+      <c r="D4" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="2">
-        <v>45383.269090057867</v>
-      </c>
-      <c r="L2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3">
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5">
         <v>2000004</v>
       </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="1">
-        <v>45574</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1">
+        <v>45724</v>
+      </c>
+      <c r="D5" t="s">
         <v>20</v>
       </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2000005</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="1">
+        <v>45747</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2000006</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="1">
+        <v>45765</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2000007</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="1">
+        <v>45767</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>2000008</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="1">
+        <v>45768</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2000009</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="1">
+        <v>45778</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2000010</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="1">
+        <v>45811</v>
+      </c>
+      <c r="D11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2000011</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="1">
+        <v>45815</v>
+      </c>
+      <c r="D12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2000012</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="1">
+        <v>45817</v>
+      </c>
+      <c r="D13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2000013</v>
+      </c>
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="1">
+        <v>45939</v>
+      </c>
+      <c r="D14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2000014</v>
+      </c>
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="1">
+        <v>46016</v>
+      </c>
+      <c r="D15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2000015</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="1">
+        <v>46017</v>
+      </c>
+      <c r="D16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2000016</v>
+      </c>
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="1">
+        <v>46023</v>
+      </c>
+      <c r="D17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2000017</v>
+      </c>
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="1">
+        <v>46048</v>
+      </c>
+      <c r="D18" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="2">
-        <v>45343.546183009261</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="E18" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2000018</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="1">
+        <v>46069</v>
+      </c>
+      <c r="D19" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="2">
-        <v>45386.406984606481</v>
-      </c>
-      <c r="L3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>2000005</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="1">
-        <v>45651</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2000019</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="1">
+        <v>46089</v>
+      </c>
+      <c r="D20" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2000020</v>
+      </c>
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="1">
+        <v>46101</v>
+      </c>
+      <c r="D21" t="s">
         <v>21</v>
       </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="E21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2000021</v>
+      </c>
+      <c r="B22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="1">
+        <v>46115</v>
+      </c>
+      <c r="D22" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2000022</v>
+      </c>
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="1">
+        <v>46117</v>
+      </c>
+      <c r="D23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2000023</v>
+      </c>
+      <c r="B24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="1">
+        <v>46118</v>
+      </c>
+      <c r="D24" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" t="s">
+        <v>17</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2000024</v>
+      </c>
+      <c r="B25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="1">
+        <v>46143</v>
+      </c>
+      <c r="D25" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" t="s">
+        <v>15</v>
+      </c>
+      <c r="F25" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" t="s">
+        <v>17</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2000025</v>
+      </c>
+      <c r="B26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="1">
+        <v>46169</v>
+      </c>
+      <c r="D26" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" t="b">
+        <v>1</v>
+      </c>
+      <c r="H26" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>2000026</v>
+      </c>
+      <c r="B27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="1">
+        <v>46176</v>
+      </c>
+      <c r="D27" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2000027</v>
+      </c>
+      <c r="B28" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" s="1">
+        <v>46182</v>
+      </c>
+      <c r="D28" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F28" t="s">
+        <v>16</v>
+      </c>
+      <c r="G28" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" t="s">
+        <v>17</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>2000028</v>
+      </c>
+      <c r="B29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="1">
+        <v>46304</v>
+      </c>
+      <c r="D29" t="s">
+        <v>29</v>
+      </c>
+      <c r="E29" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G29" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" t="s">
+        <v>17</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>2000029</v>
+      </c>
+      <c r="B30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" s="1">
+        <v>46381</v>
+      </c>
+      <c r="D30" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" t="s">
+        <v>15</v>
+      </c>
+      <c r="F30" t="s">
+        <v>16</v>
+      </c>
+      <c r="G30" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" t="s">
+        <v>17</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>2000030</v>
+      </c>
+      <c r="B31" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="1">
+        <v>46382</v>
+      </c>
+      <c r="D31" t="s">
+        <v>31</v>
+      </c>
+      <c r="E31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" t="s">
+        <v>16</v>
+      </c>
+      <c r="G31" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" t="s">
+        <v>17</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>2000031</v>
+      </c>
+      <c r="B32" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" s="1">
+        <v>46388</v>
+      </c>
+      <c r="D32" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" t="s">
+        <v>15</v>
+      </c>
+      <c r="F32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" t="s">
+        <v>17</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>2000032</v>
+      </c>
+      <c r="B33" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="1">
+        <v>46413</v>
+      </c>
+      <c r="D33" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="2">
-        <v>45343.546183009261</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="E33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F33" t="s">
+        <v>16</v>
+      </c>
+      <c r="G33" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" t="s">
+        <v>17</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>2000033</v>
+      </c>
+      <c r="B34" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" s="1">
+        <v>46434</v>
+      </c>
+      <c r="D34" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="2">
-        <v>45386.407227847223</v>
-      </c>
-      <c r="L4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>2000003</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1">
-        <v>45405</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E34" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" t="s">
+        <v>16</v>
+      </c>
+      <c r="G34" t="b">
+        <v>1</v>
+      </c>
+      <c r="H34" t="s">
+        <v>17</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>2000034</v>
+      </c>
+      <c r="B35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="1">
+        <v>46454</v>
+      </c>
+      <c r="D35" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35" t="s">
+        <v>16</v>
+      </c>
+      <c r="G35" t="b">
+        <v>1</v>
+      </c>
+      <c r="H35" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>2000035</v>
+      </c>
+      <c r="B36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" s="1">
+        <v>46456</v>
+      </c>
+      <c r="D36" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" t="s">
+        <v>15</v>
+      </c>
+      <c r="F36" t="s">
+        <v>16</v>
+      </c>
+      <c r="G36" t="b">
+        <v>1</v>
+      </c>
+      <c r="H36" t="s">
+        <v>17</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>2000036</v>
+      </c>
+      <c r="B37" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="1">
+        <v>46472</v>
+      </c>
+      <c r="D37" t="s">
         <v>22</v>
       </c>
-      <c r="E5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="E37" t="s">
+        <v>15</v>
+      </c>
+      <c r="F37" t="s">
+        <v>16</v>
+      </c>
+      <c r="G37" t="b">
+        <v>1</v>
+      </c>
+      <c r="H37" t="s">
+        <v>17</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>2000037</v>
+      </c>
+      <c r="B38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="1">
+        <v>46474</v>
+      </c>
+      <c r="D38" t="s">
+        <v>23</v>
+      </c>
+      <c r="E38" t="s">
+        <v>15</v>
+      </c>
+      <c r="F38" t="s">
+        <v>16</v>
+      </c>
+      <c r="G38" t="b">
+        <v>1</v>
+      </c>
+      <c r="H38" t="s">
+        <v>17</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>2000038</v>
+      </c>
+      <c r="B39" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" s="1">
+        <v>46475</v>
+      </c>
+      <c r="D39" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" t="s">
+        <v>15</v>
+      </c>
+      <c r="F39" t="s">
+        <v>16</v>
+      </c>
+      <c r="G39" t="b">
+        <v>1</v>
+      </c>
+      <c r="H39" t="s">
+        <v>17</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>2000039</v>
+      </c>
+      <c r="B40" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" s="1">
+        <v>46508</v>
+      </c>
+      <c r="D40" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" t="s">
+        <v>15</v>
+      </c>
+      <c r="F40" t="s">
+        <v>16</v>
+      </c>
+      <c r="G40" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" t="s">
+        <v>17</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>2000040</v>
+      </c>
+      <c r="B41" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" s="1">
+        <v>46524</v>
+      </c>
+      <c r="D41" t="s">
+        <v>27</v>
+      </c>
+      <c r="E41" t="s">
+        <v>15</v>
+      </c>
+      <c r="F41" t="s">
+        <v>16</v>
+      </c>
+      <c r="G41" t="b">
+        <v>1</v>
+      </c>
+      <c r="H41" t="s">
+        <v>17</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>2000041</v>
+      </c>
+      <c r="B42" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" s="1">
+        <v>46541</v>
+      </c>
+      <c r="D42" t="s">
+        <v>26</v>
+      </c>
+      <c r="E42" t="s">
+        <v>15</v>
+      </c>
+      <c r="F42" t="s">
+        <v>16</v>
+      </c>
+      <c r="G42" t="b">
+        <v>1</v>
+      </c>
+      <c r="H42" t="s">
+        <v>17</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>2000042</v>
+      </c>
+      <c r="B43" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="1">
+        <v>46547</v>
+      </c>
+      <c r="D43" t="s">
+        <v>28</v>
+      </c>
+      <c r="E43" t="s">
+        <v>15</v>
+      </c>
+      <c r="F43" t="s">
+        <v>16</v>
+      </c>
+      <c r="G43" t="b">
+        <v>1</v>
+      </c>
+      <c r="H43" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>2000043</v>
+      </c>
+      <c r="B44" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="1">
+        <v>46669</v>
+      </c>
+      <c r="D44" t="s">
+        <v>29</v>
+      </c>
+      <c r="E44" t="s">
+        <v>15</v>
+      </c>
+      <c r="F44" t="s">
+        <v>16</v>
+      </c>
+      <c r="G44" t="b">
+        <v>1</v>
+      </c>
+      <c r="H44" t="s">
+        <v>17</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>2000044</v>
+      </c>
+      <c r="B45" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" s="1">
+        <v>46746</v>
+      </c>
+      <c r="D45" t="s">
+        <v>30</v>
+      </c>
+      <c r="E45" t="s">
+        <v>15</v>
+      </c>
+      <c r="F45" t="s">
+        <v>16</v>
+      </c>
+      <c r="G45" t="b">
+        <v>1</v>
+      </c>
+      <c r="H45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>2000045</v>
+      </c>
+      <c r="B46" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" s="1">
+        <v>46747</v>
+      </c>
+      <c r="D46" t="s">
+        <v>31</v>
+      </c>
+      <c r="E46" t="s">
+        <v>15</v>
+      </c>
+      <c r="F46" t="s">
+        <v>16</v>
+      </c>
+      <c r="G46" t="b">
+        <v>1</v>
+      </c>
+      <c r="H46" t="s">
+        <v>17</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L46" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>2000046</v>
+      </c>
+      <c r="B47" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" s="1">
+        <v>46753</v>
+      </c>
+      <c r="D47" t="s">
+        <v>14</v>
+      </c>
+      <c r="E47" t="s">
+        <v>15</v>
+      </c>
+      <c r="F47" t="s">
+        <v>16</v>
+      </c>
+      <c r="G47" t="b">
+        <v>1</v>
+      </c>
+      <c r="H47" t="s">
+        <v>17</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>2000047</v>
+      </c>
+      <c r="B48" t="s">
+        <v>13</v>
+      </c>
+      <c r="C48" s="1">
+        <v>46778</v>
+      </c>
+      <c r="D48" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="2">
-        <v>45343.546183009261</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="E48" t="s">
+        <v>15</v>
+      </c>
+      <c r="F48" t="s">
+        <v>16</v>
+      </c>
+      <c r="G48" t="b">
+        <v>1</v>
+      </c>
+      <c r="H48" t="s">
+        <v>17</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>2000048</v>
+      </c>
+      <c r="B49" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="1">
+        <v>46799</v>
+      </c>
+      <c r="D49" t="s">
         <v>19</v>
       </c>
-      <c r="K5" s="2">
-        <v>45386.407439363429</v>
-      </c>
-      <c r="L5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>2000001</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="1">
-        <v>45292</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="E49" t="s">
+        <v>15</v>
+      </c>
+      <c r="F49" t="s">
+        <v>16</v>
+      </c>
+      <c r="G49" t="b">
+        <v>1</v>
+      </c>
+      <c r="H49" t="s">
+        <v>17</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L49" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>2000049</v>
+      </c>
+      <c r="B50" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="1">
+        <v>46810</v>
+      </c>
+      <c r="D50" t="s">
+        <v>21</v>
+      </c>
+      <c r="E50" t="s">
+        <v>15</v>
+      </c>
+      <c r="F50" t="s">
+        <v>16</v>
+      </c>
+      <c r="G50" t="b">
+        <v>1</v>
+      </c>
+      <c r="H50" t="s">
+        <v>17</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>2000050</v>
+      </c>
+      <c r="B51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="1">
+        <v>46820</v>
+      </c>
+      <c r="D51" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" t="s">
+        <v>15</v>
+      </c>
+      <c r="F51" t="s">
+        <v>16</v>
+      </c>
+      <c r="G51" t="b">
+        <v>1</v>
+      </c>
+      <c r="H51" t="s">
+        <v>17</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>2000051</v>
+      </c>
+      <c r="B52" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="1">
+        <v>46857</v>
+      </c>
+      <c r="D52" t="s">
+        <v>22</v>
+      </c>
+      <c r="E52" t="s">
+        <v>15</v>
+      </c>
+      <c r="F52" t="s">
+        <v>16</v>
+      </c>
+      <c r="G52" t="b">
+        <v>1</v>
+      </c>
+      <c r="H52" t="s">
+        <v>17</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>2000052</v>
+      </c>
+      <c r="B53" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" s="1">
+        <v>46859</v>
+      </c>
+      <c r="D53" t="s">
         <v>23</v>
       </c>
-      <c r="E6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="E53" t="s">
+        <v>15</v>
+      </c>
+      <c r="F53" t="s">
+        <v>16</v>
+      </c>
+      <c r="G53" t="b">
+        <v>1</v>
+      </c>
+      <c r="H53" t="s">
+        <v>17</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>2000053</v>
+      </c>
+      <c r="B54" t="s">
+        <v>13</v>
+      </c>
+      <c r="C54" s="1">
+        <v>46860</v>
+      </c>
+      <c r="D54" t="s">
+        <v>24</v>
+      </c>
+      <c r="E54" t="s">
+        <v>15</v>
+      </c>
+      <c r="F54" t="s">
+        <v>16</v>
+      </c>
+      <c r="G54" t="b">
+        <v>1</v>
+      </c>
+      <c r="H54" t="s">
+        <v>17</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>2000054</v>
+      </c>
+      <c r="B55" t="s">
+        <v>13</v>
+      </c>
+      <c r="C55" s="1">
+        <v>46874</v>
+      </c>
+      <c r="D55" t="s">
+        <v>25</v>
+      </c>
+      <c r="E55" t="s">
+        <v>15</v>
+      </c>
+      <c r="F55" t="s">
+        <v>16</v>
+      </c>
+      <c r="G55" t="b">
+        <v>1</v>
+      </c>
+      <c r="H55" t="s">
+        <v>17</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>2000055</v>
+      </c>
+      <c r="B56" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" s="1">
+        <v>46878</v>
+      </c>
+      <c r="D56" t="s">
+        <v>27</v>
+      </c>
+      <c r="E56" t="s">
+        <v>15</v>
+      </c>
+      <c r="F56" t="s">
+        <v>16</v>
+      </c>
+      <c r="G56" t="b">
+        <v>1</v>
+      </c>
+      <c r="H56" t="s">
+        <v>17</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>2000056</v>
+      </c>
+      <c r="B57" t="s">
+        <v>13</v>
+      </c>
+      <c r="C57" s="1">
+        <v>46907</v>
+      </c>
+      <c r="D57" t="s">
+        <v>26</v>
+      </c>
+      <c r="E57" t="s">
+        <v>15</v>
+      </c>
+      <c r="F57" t="s">
+        <v>16</v>
+      </c>
+      <c r="G57" t="b">
+        <v>1</v>
+      </c>
+      <c r="H57" t="s">
+        <v>17</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>2000057</v>
+      </c>
+      <c r="B58" t="s">
+        <v>13</v>
+      </c>
+      <c r="C58" s="1">
+        <v>46913</v>
+      </c>
+      <c r="D58" t="s">
+        <v>28</v>
+      </c>
+      <c r="E58" t="s">
+        <v>15</v>
+      </c>
+      <c r="F58" t="s">
+        <v>16</v>
+      </c>
+      <c r="G58" t="b">
+        <v>1</v>
+      </c>
+      <c r="H58" t="s">
+        <v>17</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>2000058</v>
+      </c>
+      <c r="B59" t="s">
+        <v>13</v>
+      </c>
+      <c r="C59" s="1">
+        <v>47035</v>
+      </c>
+      <c r="D59" t="s">
+        <v>29</v>
+      </c>
+      <c r="E59" t="s">
+        <v>15</v>
+      </c>
+      <c r="F59" t="s">
+        <v>16</v>
+      </c>
+      <c r="G59" t="b">
+        <v>1</v>
+      </c>
+      <c r="H59" t="s">
+        <v>17</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>2000059</v>
+      </c>
+      <c r="B60" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="1">
+        <v>47112</v>
+      </c>
+      <c r="D60" t="s">
+        <v>30</v>
+      </c>
+      <c r="E60" t="s">
+        <v>15</v>
+      </c>
+      <c r="F60" t="s">
+        <v>16</v>
+      </c>
+      <c r="G60" t="b">
+        <v>1</v>
+      </c>
+      <c r="H60" t="s">
+        <v>17</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>2000060</v>
+      </c>
+      <c r="B61" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="1">
+        <v>47113</v>
+      </c>
+      <c r="D61" t="s">
+        <v>31</v>
+      </c>
+      <c r="E61" t="s">
+        <v>15</v>
+      </c>
+      <c r="F61" t="s">
+        <v>16</v>
+      </c>
+      <c r="G61" t="b">
+        <v>1</v>
+      </c>
+      <c r="H61" t="s">
+        <v>17</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>2000061</v>
+      </c>
+      <c r="B62" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="1">
+        <v>47119</v>
+      </c>
+      <c r="D62" t="s">
+        <v>14</v>
+      </c>
+      <c r="E62" t="s">
+        <v>15</v>
+      </c>
+      <c r="F62" t="s">
+        <v>16</v>
+      </c>
+      <c r="G62" t="b">
+        <v>1</v>
+      </c>
+      <c r="H62" t="s">
+        <v>17</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>2000062</v>
+      </c>
+      <c r="B63" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="1">
+        <v>47144</v>
+      </c>
+      <c r="D63" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="2">
-        <v>45343.546183009261</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="E63" t="s">
+        <v>15</v>
+      </c>
+      <c r="F63" t="s">
+        <v>16</v>
+      </c>
+      <c r="G63" t="b">
+        <v>1</v>
+      </c>
+      <c r="H63" t="s">
+        <v>17</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>2000063</v>
+      </c>
+      <c r="B64" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="1">
+        <v>47164</v>
+      </c>
+      <c r="D64" t="s">
+        <v>21</v>
+      </c>
+      <c r="E64" t="s">
+        <v>15</v>
+      </c>
+      <c r="F64" t="s">
+        <v>16</v>
+      </c>
+      <c r="G64" t="b">
+        <v>1</v>
+      </c>
+      <c r="H64" t="s">
+        <v>17</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>2000064</v>
+      </c>
+      <c r="B65" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="1">
+        <v>47165</v>
+      </c>
+      <c r="D65" t="s">
         <v>19</v>
       </c>
-      <c r="K6" s="2">
-        <v>45386.407598043981</v>
-      </c>
-      <c r="L6" t="s">
-        <v>17</v>
+      <c r="E65" t="s">
+        <v>15</v>
+      </c>
+      <c r="F65" t="s">
+        <v>16</v>
+      </c>
+      <c r="G65" t="b">
+        <v>1</v>
+      </c>
+      <c r="H65" t="s">
+        <v>17</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>2000065</v>
+      </c>
+      <c r="B66" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" s="1">
+        <v>47185</v>
+      </c>
+      <c r="D66" t="s">
+        <v>20</v>
+      </c>
+      <c r="E66" t="s">
+        <v>15</v>
+      </c>
+      <c r="F66" t="s">
+        <v>16</v>
+      </c>
+      <c r="G66" t="b">
+        <v>1</v>
+      </c>
+      <c r="H66" t="s">
+        <v>17</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>2000066</v>
+      </c>
+      <c r="B67" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" s="1">
+        <v>47207</v>
+      </c>
+      <c r="D67" t="s">
+        <v>22</v>
+      </c>
+      <c r="E67" t="s">
+        <v>15</v>
+      </c>
+      <c r="F67" t="s">
+        <v>16</v>
+      </c>
+      <c r="G67" t="b">
+        <v>1</v>
+      </c>
+      <c r="H67" t="s">
+        <v>17</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>2000067</v>
+      </c>
+      <c r="B68" t="s">
+        <v>13</v>
+      </c>
+      <c r="C68" s="1">
+        <v>47209</v>
+      </c>
+      <c r="D68" t="s">
+        <v>23</v>
+      </c>
+      <c r="E68" t="s">
+        <v>15</v>
+      </c>
+      <c r="F68" t="s">
+        <v>16</v>
+      </c>
+      <c r="G68" t="b">
+        <v>1</v>
+      </c>
+      <c r="H68" t="s">
+        <v>17</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>2000068</v>
+      </c>
+      <c r="B69" t="s">
+        <v>13</v>
+      </c>
+      <c r="C69" s="1">
+        <v>47210</v>
+      </c>
+      <c r="D69" t="s">
+        <v>24</v>
+      </c>
+      <c r="E69" t="s">
+        <v>15</v>
+      </c>
+      <c r="F69" t="s">
+        <v>16</v>
+      </c>
+      <c r="G69" t="b">
+        <v>1</v>
+      </c>
+      <c r="H69" t="s">
+        <v>17</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>2000069</v>
+      </c>
+      <c r="B70" t="s">
+        <v>13</v>
+      </c>
+      <c r="C70" s="1">
+        <v>47232</v>
+      </c>
+      <c r="D70" t="s">
+        <v>27</v>
+      </c>
+      <c r="E70" t="s">
+        <v>15</v>
+      </c>
+      <c r="F70" t="s">
+        <v>16</v>
+      </c>
+      <c r="G70" t="b">
+        <v>1</v>
+      </c>
+      <c r="H70" t="s">
+        <v>17</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>2000070</v>
+      </c>
+      <c r="B71" t="s">
+        <v>13</v>
+      </c>
+      <c r="C71" s="1">
+        <v>47239</v>
+      </c>
+      <c r="D71" t="s">
+        <v>25</v>
+      </c>
+      <c r="E71" t="s">
+        <v>15</v>
+      </c>
+      <c r="F71" t="s">
+        <v>16</v>
+      </c>
+      <c r="G71" t="b">
+        <v>1</v>
+      </c>
+      <c r="H71" t="s">
+        <v>17</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L71" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>2000071</v>
+      </c>
+      <c r="B72" t="s">
+        <v>13</v>
+      </c>
+      <c r="C72" s="1">
+        <v>47272</v>
+      </c>
+      <c r="D72" t="s">
+        <v>26</v>
+      </c>
+      <c r="E72" t="s">
+        <v>15</v>
+      </c>
+      <c r="F72" t="s">
+        <v>16</v>
+      </c>
+      <c r="G72" t="b">
+        <v>1</v>
+      </c>
+      <c r="H72" t="s">
+        <v>17</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L72" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>2000072</v>
+      </c>
+      <c r="B73" t="s">
+        <v>13</v>
+      </c>
+      <c r="C73" s="1">
+        <v>47278</v>
+      </c>
+      <c r="D73" t="s">
+        <v>28</v>
+      </c>
+      <c r="E73" t="s">
+        <v>15</v>
+      </c>
+      <c r="F73" t="s">
+        <v>16</v>
+      </c>
+      <c r="G73" t="b">
+        <v>1</v>
+      </c>
+      <c r="H73" t="s">
+        <v>17</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L73" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>2000073</v>
+      </c>
+      <c r="B74" t="s">
+        <v>13</v>
+      </c>
+      <c r="C74" s="1">
+        <v>47400</v>
+      </c>
+      <c r="D74" t="s">
+        <v>29</v>
+      </c>
+      <c r="E74" t="s">
+        <v>15</v>
+      </c>
+      <c r="F74" t="s">
+        <v>16</v>
+      </c>
+      <c r="G74" t="b">
+        <v>1</v>
+      </c>
+      <c r="H74" t="s">
+        <v>17</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L74" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>2000074</v>
+      </c>
+      <c r="B75" t="s">
+        <v>13</v>
+      </c>
+      <c r="C75" s="1">
+        <v>47477</v>
+      </c>
+      <c r="D75" t="s">
+        <v>30</v>
+      </c>
+      <c r="E75" t="s">
+        <v>15</v>
+      </c>
+      <c r="F75" t="s">
+        <v>16</v>
+      </c>
+      <c r="G75" t="b">
+        <v>1</v>
+      </c>
+      <c r="H75" t="s">
+        <v>17</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L75" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>2000075</v>
+      </c>
+      <c r="B76" t="s">
+        <v>13</v>
+      </c>
+      <c r="C76" s="1">
+        <v>47478</v>
+      </c>
+      <c r="D76" t="s">
+        <v>31</v>
+      </c>
+      <c r="E76" t="s">
+        <v>15</v>
+      </c>
+      <c r="F76" t="s">
+        <v>16</v>
+      </c>
+      <c r="G76" t="b">
+        <v>1</v>
+      </c>
+      <c r="H76" t="s">
+        <v>17</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L76" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
